--- a/interview_forms/040_nonprofit_fundraising_manager_interview_form--interview_forms.xlsx
+++ b/interview_forms/040_nonprofit_fundraising_manager_interview_form--interview_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -533,30 +543,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>experience_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Years of Experience</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -567,14 +577,14 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -590,99 +600,168 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>communication_method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>Preferred Communication</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>fundraising_campaigns</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Fundraising Campaigns</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Primary Contact</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nonprofit_fundraising_manager_interview_form</t>
+          <t>communication_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit Fundraising Manager Interview Form</t>
+          <t>Communication Frequency</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>challenges</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Challenges</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>success_measures</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Success Measures</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>favorite_resources</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Favorite Resource</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -692,6 +771,467 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>high_school</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>bachelor's</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bachelor's</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>master's</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Master's</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>doctoral</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Doctoral</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>skills_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>grant_writing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Grant Writing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>skills_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>skills_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>event_planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Event Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>skills_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>volunteer_management</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Volunteer Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>skills_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>budgeting</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Budgeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>in-person_meeting</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>In-person meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fundraising_campaigns_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>awareness</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fundraising_campaigns_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fundraising_campaigns_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>special_events</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Special Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fundraising_campaigns_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fundraising_campaigns_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>grants</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>contact_person_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ceo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>contact_person_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>board_member</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Board Member</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>contact_person_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>marketing_manager</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>contact_person_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>development_director</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Development Director</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>contact_person_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>volunteer_coordinator</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Volunteer Coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>communication_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>communication_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>communication_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
